--- a/Cronograma/Itinerario _PPP_V6.0.xlsx
+++ b/Cronograma/Itinerario _PPP_V6.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plusm\Desktop\PPP\37009-PPP\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10B130AC-17E0-4C91-9288-E0A5F6B94FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729DFA87-3BB7-44F7-959E-82190019B0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -626,11 +626,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -678,67 +704,12 @@
         </x:ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -752,8 +723,75 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3969,15 +4007,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.7">
-      <c r="B1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="B1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
@@ -4034,21 +4072,21 @@
         <v>9</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="27">
+      <c r="A9" s="30">
         <v>46286</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="42" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -4057,14 +4095,14 @@
       <c r="D9" s="10">
         <v>3</v>
       </c>
-      <c r="E9" s="30">
-        <f>SUM(D9:D12)</f>
-        <v>12</v>
-      </c>
-      <c r="F9" s="35" t="s">
+      <c r="E9" s="42">
+        <f>SUM(D9:D10)</f>
+        <v>6</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="33">
         <v>6</v>
       </c>
       <c r="H9" s="12"/>
@@ -4073,36 +4111,36 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="27"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="10">
         <v>3</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="22"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="12"/>
       <c r="I10" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="27">
+      <c r="A11" s="30">
         <v>46287</v>
       </c>
-      <c r="B11" s="22"/>
+      <c r="B11" s="42"/>
       <c r="C11" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="10">
         <v>3</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="22">
+      <c r="E11" s="9"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="33">
         <v>6</v>
       </c>
       <c r="H11" s="12"/>
@@ -4111,27 +4149,27 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="27"/>
-      <c r="B12" s="22"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="10">
         <v>3</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="22"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="12"/>
       <c r="I12" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="27">
+      <c r="A13" s="30">
         <v>46288</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="42" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -4140,14 +4178,14 @@
       <c r="D13" s="10">
         <v>3</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="33">
         <f>SUM(D13:D20)</f>
         <v>24</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="33">
         <v>6</v>
       </c>
       <c r="H13" s="12"/>
@@ -4156,36 +4194,36 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="27"/>
-      <c r="B14" s="22"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="43"/>
       <c r="C14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="10">
         <v>3</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="22"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="12"/>
       <c r="I14" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="27">
+      <c r="A15" s="30">
         <v>46289</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="44"/>
       <c r="C15" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="10">
         <v>3</v>
       </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="22">
+      <c r="E15" s="33"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="33">
         <v>6</v>
       </c>
       <c r="H15" s="12"/>
@@ -4194,36 +4232,36 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="27"/>
-      <c r="B16" s="22"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="10">
         <v>3</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="22"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="33"/>
       <c r="H16" s="12"/>
       <c r="I16" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="27">
+      <c r="A17" s="30">
         <v>46290</v>
       </c>
-      <c r="B17" s="22"/>
+      <c r="B17" s="42"/>
       <c r="C17" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="10">
         <v>3</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="22">
+      <c r="E17" s="33"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="33">
         <v>6</v>
       </c>
       <c r="H17" s="12"/>
@@ -4232,36 +4270,36 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="27"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="10">
         <v>3</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="12"/>
       <c r="I18" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="27">
+      <c r="A19" s="30">
         <v>46293</v>
       </c>
-      <c r="B19" s="22"/>
+      <c r="B19" s="42"/>
       <c r="C19" s="10" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="10">
         <v>3</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="22">
+      <c r="E19" s="33"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="33">
         <v>6</v>
       </c>
       <c r="H19" s="12"/>
@@ -4270,27 +4308,27 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="27"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="10">
         <v>3</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="33"/>
       <c r="H20" s="12"/>
       <c r="I20" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="27">
+      <c r="A21" s="30">
         <v>46294</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="42" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -4299,14 +4337,14 @@
       <c r="D21" s="10">
         <v>3</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="33">
         <f>SUM(D21:D34)</f>
         <v>42</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="33">
         <v>6</v>
       </c>
       <c r="H21" s="12"/>
@@ -4315,36 +4353,36 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="27"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="10">
         <v>3</v>
       </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="22"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="33"/>
       <c r="H22" s="12"/>
       <c r="I22" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="27">
+      <c r="A23" s="30">
         <v>46295</v>
       </c>
-      <c r="B23" s="22"/>
+      <c r="B23" s="42"/>
       <c r="C23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="10">
         <v>3</v>
       </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="22">
+      <c r="E23" s="33"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="33">
         <v>6</v>
       </c>
       <c r="H23" s="12"/>
@@ -4353,36 +4391,36 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="27"/>
-      <c r="B24" s="22"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="43"/>
       <c r="C24" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D24" s="10">
         <v>3</v>
       </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="22"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="12"/>
       <c r="I24" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="27">
+      <c r="A25" s="30">
         <v>46296</v>
       </c>
-      <c r="B25" s="22"/>
+      <c r="B25" s="42"/>
       <c r="C25" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D25" s="10">
         <v>3</v>
       </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="22">
+      <c r="E25" s="33"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="33">
         <v>6</v>
       </c>
       <c r="H25" s="12"/>
@@ -4391,36 +4429,36 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="27"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="43"/>
       <c r="C26" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="10">
         <v>3</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="22"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="33"/>
       <c r="H26" s="12"/>
       <c r="I26" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="27">
+      <c r="A27" s="30">
         <v>46297</v>
       </c>
-      <c r="B27" s="22"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D27" s="10">
         <v>3</v>
       </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="22">
+      <c r="E27" s="33"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="33">
         <v>6</v>
       </c>
       <c r="H27" s="12"/>
@@ -4429,36 +4467,36 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="27"/>
-      <c r="B28" s="22"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="43"/>
       <c r="C28" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D28" s="10">
         <v>3</v>
       </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="22"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="33"/>
       <c r="H28" s="12"/>
       <c r="I28" s="14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="27">
+      <c r="A29" s="30">
         <v>46300</v>
       </c>
-      <c r="B29" s="22"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D29" s="10">
         <v>3</v>
       </c>
-      <c r="E29" s="30"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="22">
+      <c r="E29" s="33"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="33">
         <v>6</v>
       </c>
       <c r="H29" s="12"/>
@@ -4467,36 +4505,36 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="27"/>
-      <c r="B30" s="22"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="43"/>
       <c r="C30" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="10">
         <v>3</v>
       </c>
-      <c r="E30" s="30"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="22"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="12"/>
       <c r="I30" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="27">
+      <c r="A31" s="30">
         <v>46301</v>
       </c>
-      <c r="B31" s="22"/>
+      <c r="B31" s="42"/>
       <c r="C31" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D31" s="10">
         <v>3</v>
       </c>
-      <c r="E31" s="30"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="22">
+      <c r="E31" s="33"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="33">
         <v>6</v>
       </c>
       <c r="H31" s="12"/>
@@ -4505,36 +4543,36 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="27"/>
-      <c r="B32" s="22"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D32" s="10">
         <v>3</v>
       </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="22"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="12"/>
       <c r="I32" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="27">
+      <c r="A33" s="30">
         <v>46302</v>
       </c>
-      <c r="B33" s="22"/>
+      <c r="B33" s="42"/>
       <c r="C33" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D33" s="10">
         <v>3</v>
       </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="22">
+      <c r="E33" s="33"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="33">
         <v>6</v>
       </c>
       <c r="H33" s="12"/>
@@ -4543,27 +4581,27 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="27"/>
-      <c r="B34" s="22"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="43"/>
       <c r="C34" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D34" s="10">
         <v>3</v>
       </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="22"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="12"/>
       <c r="I34" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="27">
+      <c r="A35" s="30">
         <v>46303</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C35" s="10" t="s">
@@ -4572,14 +4610,14 @@
       <c r="D35" s="10">
         <v>3</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="33">
         <f>SUM(D35:D46)</f>
         <v>36</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="33">
         <v>6</v>
       </c>
       <c r="H35" s="12"/>
@@ -4588,36 +4626,36 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="27"/>
-      <c r="B36" s="22"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="10" t="s">
         <v>46</v>
       </c>
       <c r="D36" s="10">
         <v>3</v>
       </c>
-      <c r="E36" s="30"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="22"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="12"/>
       <c r="I36" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="27">
+      <c r="A37" s="30">
         <v>46307</v>
       </c>
-      <c r="B37" s="23"/>
+      <c r="B37" s="40"/>
       <c r="C37" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D37" s="10">
         <v>3</v>
       </c>
-      <c r="E37" s="30"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="22">
+      <c r="E37" s="33"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="33">
         <v>6</v>
       </c>
       <c r="H37" s="12"/>
@@ -4626,36 +4664,36 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="27"/>
-      <c r="B38" s="23"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="40"/>
       <c r="C38" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D38" s="10">
         <v>3</v>
       </c>
-      <c r="E38" s="30"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="22"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="33"/>
       <c r="H38" s="12"/>
       <c r="I38" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="27">
+      <c r="A39" s="30">
         <v>46308</v>
       </c>
-      <c r="B39" s="22"/>
+      <c r="B39" s="33"/>
       <c r="C39" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D39" s="10">
         <v>3</v>
       </c>
-      <c r="E39" s="30"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="22">
+      <c r="E39" s="33"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="33">
         <v>6</v>
       </c>
       <c r="H39" s="12"/>
@@ -4664,36 +4702,36 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A40" s="27"/>
-      <c r="B40" s="22"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="33"/>
       <c r="C40" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D40" s="10">
         <v>3</v>
       </c>
-      <c r="E40" s="30"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="22"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="33"/>
       <c r="H40" s="12"/>
       <c r="I40" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="27">
+      <c r="A41" s="30">
         <v>46309</v>
       </c>
-      <c r="B41" s="22"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="10" t="s">
         <v>51</v>
       </c>
       <c r="D41" s="10">
         <v>3</v>
       </c>
-      <c r="E41" s="30"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="22">
+      <c r="E41" s="33"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="33">
         <v>6</v>
       </c>
       <c r="H41" s="12"/>
@@ -4702,36 +4740,36 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="27"/>
-      <c r="B42" s="22"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="33"/>
       <c r="C42" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D42" s="10">
         <v>3</v>
       </c>
-      <c r="E42" s="30"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="22"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="33"/>
       <c r="H42" s="12"/>
       <c r="I42" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="27">
+      <c r="A43" s="30">
         <v>46310</v>
       </c>
-      <c r="B43" s="22"/>
+      <c r="B43" s="33"/>
       <c r="C43" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D43" s="10">
         <v>3</v>
       </c>
-      <c r="E43" s="30"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="22">
+      <c r="E43" s="33"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="33">
         <v>6</v>
       </c>
       <c r="H43" s="12"/>
@@ -4740,36 +4778,36 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A44" s="27"/>
-      <c r="B44" s="22"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="33"/>
       <c r="C44" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D44" s="10">
         <v>3</v>
       </c>
-      <c r="E44" s="30"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="22"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="33"/>
       <c r="H44" s="12"/>
       <c r="I44" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A45" s="27">
+      <c r="A45" s="30">
         <v>46311</v>
       </c>
-      <c r="B45" s="22"/>
+      <c r="B45" s="33"/>
       <c r="C45" s="10" t="s">
         <v>55</v>
       </c>
       <c r="D45" s="10">
         <v>3</v>
       </c>
-      <c r="E45" s="30"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="22">
+      <c r="E45" s="33"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="33">
         <v>6</v>
       </c>
       <c r="H45" s="12"/>
@@ -4778,27 +4816,27 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A46" s="27"/>
-      <c r="B46" s="22"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="33"/>
       <c r="C46" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D46" s="10">
         <v>3</v>
       </c>
-      <c r="E46" s="30"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="22"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="33"/>
       <c r="H46" s="12"/>
       <c r="I46" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A47" s="27">
+      <c r="A47" s="30">
         <v>46314</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="33" t="s">
         <v>57</v>
       </c>
       <c r="C47" s="10" t="s">
@@ -4807,14 +4845,14 @@
       <c r="D47" s="10">
         <v>3</v>
       </c>
-      <c r="E47" s="30">
+      <c r="E47" s="33">
         <f>SUM(D47:D54)</f>
         <v>24</v>
       </c>
-      <c r="F47" s="35" t="s">
+      <c r="F47" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="33">
         <v>6</v>
       </c>
       <c r="H47" s="12"/>
@@ -4823,36 +4861,36 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A48" s="27"/>
-      <c r="B48" s="22"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="33"/>
       <c r="C48" s="10" t="s">
         <v>59</v>
       </c>
       <c r="D48" s="10">
         <v>3</v>
       </c>
-      <c r="E48" s="30"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="22"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="33"/>
       <c r="H48" s="12"/>
       <c r="I48" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A49" s="27">
+      <c r="A49" s="30">
         <v>46315</v>
       </c>
-      <c r="B49" s="22"/>
+      <c r="B49" s="33"/>
       <c r="C49" s="10" t="s">
         <v>60</v>
       </c>
       <c r="D49" s="10">
         <v>3</v>
       </c>
-      <c r="E49" s="30"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="22">
+      <c r="E49" s="33"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="33">
         <v>6</v>
       </c>
       <c r="H49" s="12"/>
@@ -4861,36 +4899,36 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A50" s="27"/>
-      <c r="B50" s="22"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="33"/>
       <c r="C50" s="10" t="s">
         <v>61</v>
       </c>
       <c r="D50" s="10">
         <v>3</v>
       </c>
-      <c r="E50" s="30"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="22"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="33"/>
       <c r="H50" s="12"/>
       <c r="I50" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A51" s="27">
+      <c r="A51" s="30">
         <v>46316</v>
       </c>
-      <c r="B51" s="22"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="10" t="s">
         <v>62</v>
       </c>
       <c r="D51" s="10">
         <v>3</v>
       </c>
-      <c r="E51" s="30"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="22">
+      <c r="E51" s="33"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="33">
         <v>6</v>
       </c>
       <c r="H51" s="12"/>
@@ -4899,36 +4937,36 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A52" s="27"/>
-      <c r="B52" s="22"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="10" t="s">
         <v>63</v>
       </c>
       <c r="D52" s="10">
         <v>3</v>
       </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="22"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="33"/>
       <c r="H52" s="12"/>
       <c r="I52" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A53" s="27">
+      <c r="A53" s="30">
         <v>46317</v>
       </c>
-      <c r="B53" s="22"/>
+      <c r="B53" s="33"/>
       <c r="C53" s="10" t="s">
         <v>64</v>
       </c>
       <c r="D53" s="10">
         <v>3</v>
       </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="22">
+      <c r="E53" s="33"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="33">
         <v>6</v>
       </c>
       <c r="H53" s="12"/>
@@ -4937,27 +4975,27 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A54" s="27"/>
-      <c r="B54" s="22"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="33"/>
       <c r="C54" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D54" s="10">
         <v>3</v>
       </c>
-      <c r="E54" s="30"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="22"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="33"/>
       <c r="H54" s="12"/>
       <c r="I54" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A55" s="27">
+      <c r="A55" s="30">
         <v>46318</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="33" t="s">
         <v>66</v>
       </c>
       <c r="C55" s="10" t="s">
@@ -4966,14 +5004,14 @@
       <c r="D55" s="10">
         <v>3</v>
       </c>
-      <c r="E55" s="30">
+      <c r="E55" s="33">
         <f>SUM(D55:D62)</f>
         <v>24</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F55" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G55" s="22">
+      <c r="G55" s="33">
         <v>6</v>
       </c>
       <c r="H55" s="12"/>
@@ -4982,36 +5020,36 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A56" s="27"/>
-      <c r="B56" s="22"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="33"/>
       <c r="C56" s="10" t="s">
         <v>68</v>
       </c>
       <c r="D56" s="10">
         <v>3</v>
       </c>
-      <c r="E56" s="30"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="22"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="33"/>
       <c r="H56" s="12"/>
       <c r="I56" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A57" s="27">
+      <c r="A57" s="30">
         <v>46321</v>
       </c>
-      <c r="B57" s="22"/>
+      <c r="B57" s="33"/>
       <c r="C57" s="10" t="s">
         <v>69</v>
       </c>
       <c r="D57" s="10">
         <v>3</v>
       </c>
-      <c r="E57" s="30"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="22">
+      <c r="E57" s="33"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="33">
         <v>6</v>
       </c>
       <c r="H57" s="12"/>
@@ -5020,36 +5058,36 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A58" s="27"/>
-      <c r="B58" s="22"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="33"/>
       <c r="C58" s="10" t="s">
         <v>70</v>
       </c>
       <c r="D58" s="10">
         <v>3</v>
       </c>
-      <c r="E58" s="30"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="22"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="33"/>
       <c r="H58" s="12"/>
       <c r="I58" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A59" s="27">
+      <c r="A59" s="30">
         <v>46322</v>
       </c>
-      <c r="B59" s="22"/>
+      <c r="B59" s="33"/>
       <c r="C59" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D59" s="10">
         <v>3</v>
       </c>
-      <c r="E59" s="30"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="22">
+      <c r="E59" s="33"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="33">
         <v>6</v>
       </c>
       <c r="H59" s="12"/>
@@ -5058,36 +5096,36 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A60" s="27"/>
-      <c r="B60" s="22"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="33"/>
       <c r="C60" s="10" t="s">
         <v>72</v>
       </c>
       <c r="D60" s="10">
         <v>3</v>
       </c>
-      <c r="E60" s="30"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="22"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="33"/>
       <c r="H60" s="12"/>
       <c r="I60" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A61" s="27">
+      <c r="A61" s="30">
         <v>46323</v>
       </c>
-      <c r="B61" s="22"/>
+      <c r="B61" s="33"/>
       <c r="C61" s="10" t="s">
         <v>73</v>
       </c>
       <c r="D61" s="10">
         <v>3</v>
       </c>
-      <c r="E61" s="30"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="22">
+      <c r="E61" s="33"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="33">
         <v>6</v>
       </c>
       <c r="H61" s="12"/>
@@ -5096,27 +5134,27 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="27"/>
-      <c r="B62" s="22"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="33"/>
       <c r="C62" s="10" t="s">
         <v>74</v>
       </c>
       <c r="D62" s="10">
         <v>3</v>
       </c>
-      <c r="E62" s="30"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="22"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="33"/>
       <c r="H62" s="12"/>
       <c r="I62" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A63" s="27">
+      <c r="A63" s="30">
         <v>46324</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="33" t="s">
         <v>75</v>
       </c>
       <c r="C63" s="10" t="s">
@@ -5125,14 +5163,14 @@
       <c r="D63" s="10">
         <v>3</v>
       </c>
-      <c r="E63" s="30">
+      <c r="E63" s="33">
         <f>SUM(D63:D66)</f>
         <v>12</v>
       </c>
-      <c r="F63" s="35" t="s">
+      <c r="F63" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G63" s="22">
+      <c r="G63" s="33">
         <v>6</v>
       </c>
       <c r="H63" s="12"/>
@@ -5141,36 +5179,36 @@
       </c>
     </row>
     <row r="64" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A64" s="27"/>
-      <c r="B64" s="22"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="33"/>
       <c r="C64" s="10" t="s">
         <v>77</v>
       </c>
       <c r="D64" s="10">
         <v>3</v>
       </c>
-      <c r="E64" s="30"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="22"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="33"/>
       <c r="H64" s="12"/>
       <c r="I64" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A65" s="27">
+      <c r="A65" s="30">
         <v>46325</v>
       </c>
-      <c r="B65" s="22"/>
+      <c r="B65" s="33"/>
       <c r="C65" s="10" t="s">
         <v>78</v>
       </c>
       <c r="D65" s="10">
         <v>3</v>
       </c>
-      <c r="E65" s="30"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="22">
+      <c r="E65" s="33"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="33">
         <v>6</v>
       </c>
       <c r="H65" s="12"/>
@@ -5179,27 +5217,27 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A66" s="27"/>
-      <c r="B66" s="22"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="33"/>
       <c r="C66" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D66" s="10">
         <v>3</v>
       </c>
-      <c r="E66" s="30"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="22"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="33"/>
       <c r="H66" s="12"/>
       <c r="I66" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A67" s="27">
+      <c r="A67" s="30">
         <v>46330</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="33" t="s">
         <v>80</v>
       </c>
       <c r="C67" s="10" t="s">
@@ -5208,14 +5246,14 @@
       <c r="D67" s="10">
         <v>3</v>
       </c>
-      <c r="E67" s="30">
+      <c r="E67" s="33">
         <f>SUM(D67:D74)</f>
         <v>24</v>
       </c>
-      <c r="F67" s="35" t="s">
+      <c r="F67" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G67" s="22">
+      <c r="G67" s="33">
         <v>6</v>
       </c>
       <c r="H67" s="12"/>
@@ -5224,36 +5262,36 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A68" s="27"/>
-      <c r="B68" s="22"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="33"/>
       <c r="C68" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D68" s="10">
         <v>3</v>
       </c>
-      <c r="E68" s="30"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="22"/>
+      <c r="E68" s="33"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="33"/>
       <c r="H68" s="12"/>
       <c r="I68" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A69" s="27">
+      <c r="A69" s="30">
         <v>46331</v>
       </c>
-      <c r="B69" s="22"/>
+      <c r="B69" s="33"/>
       <c r="C69" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D69" s="10">
         <v>3</v>
       </c>
-      <c r="E69" s="30"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="22">
+      <c r="E69" s="33"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="33">
         <v>6</v>
       </c>
       <c r="H69" s="12"/>
@@ -5262,36 +5300,36 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A70" s="27"/>
-      <c r="B70" s="22"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="33"/>
       <c r="C70" s="10" t="s">
         <v>84</v>
       </c>
       <c r="D70" s="10">
         <v>3</v>
       </c>
-      <c r="E70" s="30"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="22"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="33"/>
       <c r="H70" s="12"/>
       <c r="I70" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A71" s="27">
+      <c r="A71" s="30">
         <v>46332</v>
       </c>
-      <c r="B71" s="22"/>
+      <c r="B71" s="33"/>
       <c r="C71" s="10" t="s">
         <v>85</v>
       </c>
       <c r="D71" s="10">
         <v>3</v>
       </c>
-      <c r="E71" s="30"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="22">
+      <c r="E71" s="33"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="33">
         <v>6</v>
       </c>
       <c r="H71" s="12"/>
@@ -5300,36 +5338,36 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A72" s="27"/>
-      <c r="B72" s="22"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="33"/>
       <c r="C72" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D72" s="10">
         <v>3</v>
       </c>
-      <c r="E72" s="30"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="22"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="33"/>
       <c r="H72" s="12"/>
       <c r="I72" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A73" s="27">
+      <c r="A73" s="30">
         <v>46335</v>
       </c>
-      <c r="B73" s="22"/>
+      <c r="B73" s="33"/>
       <c r="C73" s="10" t="s">
         <v>87</v>
       </c>
       <c r="D73" s="10">
         <v>3</v>
       </c>
-      <c r="E73" s="30"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="22">
+      <c r="E73" s="33"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="33">
         <v>6</v>
       </c>
       <c r="H73" s="12"/>
@@ -5338,27 +5376,27 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A74" s="27"/>
-      <c r="B74" s="22"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="33"/>
       <c r="C74" s="10" t="s">
         <v>88</v>
       </c>
       <c r="D74" s="10">
         <v>3</v>
       </c>
-      <c r="E74" s="30"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="22"/>
+      <c r="E74" s="33"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="33"/>
       <c r="H74" s="12"/>
       <c r="I74" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A75" s="27">
+      <c r="A75" s="30">
         <v>46336</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="33" t="s">
         <v>89</v>
       </c>
       <c r="C75" s="10" t="s">
@@ -5367,14 +5405,14 @@
       <c r="D75" s="10">
         <v>3</v>
       </c>
-      <c r="E75" s="30">
+      <c r="E75" s="33">
         <f>SUM(D75:D88)</f>
         <v>42</v>
       </c>
-      <c r="F75" s="35" t="s">
+      <c r="F75" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G75" s="22">
+      <c r="G75" s="33">
         <v>6</v>
       </c>
       <c r="H75" s="12"/>
@@ -5383,36 +5421,36 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A76" s="27"/>
-      <c r="B76" s="22"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="33"/>
       <c r="C76" s="10" t="s">
         <v>91</v>
       </c>
       <c r="D76" s="10">
         <v>3</v>
       </c>
-      <c r="E76" s="30"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="22"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="33"/>
       <c r="H76" s="12"/>
       <c r="I76" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A77" s="27">
+      <c r="A77" s="30">
         <v>46337</v>
       </c>
-      <c r="B77" s="22"/>
+      <c r="B77" s="33"/>
       <c r="C77" s="10" t="s">
         <v>92</v>
       </c>
       <c r="D77" s="10">
         <v>3</v>
       </c>
-      <c r="E77" s="30"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="22">
+      <c r="E77" s="33"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="33">
         <v>6</v>
       </c>
       <c r="H77" s="12"/>
@@ -5421,36 +5459,36 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A78" s="27"/>
-      <c r="B78" s="22"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="33"/>
       <c r="C78" s="10" t="s">
         <v>93</v>
       </c>
       <c r="D78" s="10">
         <v>3</v>
       </c>
-      <c r="E78" s="30"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="22"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="33"/>
       <c r="H78" s="12"/>
       <c r="I78" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A79" s="27">
+      <c r="A79" s="30">
         <v>46338</v>
       </c>
-      <c r="B79" s="22"/>
+      <c r="B79" s="33"/>
       <c r="C79" s="10" t="s">
         <v>94</v>
       </c>
       <c r="D79" s="10">
         <v>3</v>
       </c>
-      <c r="E79" s="30"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="22">
+      <c r="E79" s="33"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="33">
         <v>6</v>
       </c>
       <c r="H79" s="12"/>
@@ -5459,36 +5497,36 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A80" s="27"/>
-      <c r="B80" s="22"/>
+      <c r="A80" s="30"/>
+      <c r="B80" s="33"/>
       <c r="C80" s="10" t="s">
         <v>95</v>
       </c>
       <c r="D80" s="10">
         <v>3</v>
       </c>
-      <c r="E80" s="30"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="22"/>
+      <c r="E80" s="33"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="33"/>
       <c r="H80" s="12"/>
       <c r="I80" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A81" s="27">
+      <c r="A81" s="30">
         <v>46339</v>
       </c>
-      <c r="B81" s="22"/>
+      <c r="B81" s="33"/>
       <c r="C81" s="10" t="s">
         <v>96</v>
       </c>
       <c r="D81" s="10">
         <v>3</v>
       </c>
-      <c r="E81" s="30"/>
-      <c r="F81" s="35"/>
-      <c r="G81" s="22">
+      <c r="E81" s="33"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="33">
         <v>6</v>
       </c>
       <c r="H81" s="12"/>
@@ -5497,36 +5535,36 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A82" s="27"/>
-      <c r="B82" s="22"/>
+      <c r="A82" s="30"/>
+      <c r="B82" s="33"/>
       <c r="C82" s="10" t="s">
         <v>97</v>
       </c>
       <c r="D82" s="10">
         <v>3</v>
       </c>
-      <c r="E82" s="30"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="22"/>
+      <c r="E82" s="33"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="33"/>
       <c r="H82" s="12"/>
       <c r="I82" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A83" s="27">
+      <c r="A83" s="30">
         <v>46342</v>
       </c>
-      <c r="B83" s="22"/>
+      <c r="B83" s="33"/>
       <c r="C83" s="10" t="s">
         <v>98</v>
       </c>
       <c r="D83" s="10">
         <v>3</v>
       </c>
-      <c r="E83" s="30"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="22">
+      <c r="E83" s="33"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="33">
         <v>6</v>
       </c>
       <c r="H83" s="12"/>
@@ -5535,36 +5573,36 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A84" s="27"/>
-      <c r="B84" s="22"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="33"/>
       <c r="C84" s="10" t="s">
         <v>99</v>
       </c>
       <c r="D84" s="10">
         <v>3</v>
       </c>
-      <c r="E84" s="30"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="22"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="33"/>
       <c r="H84" s="12"/>
       <c r="I84" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A85" s="27">
+      <c r="A85" s="30">
         <v>46343</v>
       </c>
-      <c r="B85" s="22"/>
+      <c r="B85" s="33"/>
       <c r="C85" s="10" t="s">
         <v>100</v>
       </c>
       <c r="D85" s="10">
         <v>3</v>
       </c>
-      <c r="E85" s="30"/>
-      <c r="F85" s="35"/>
-      <c r="G85" s="22">
+      <c r="E85" s="33"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="33">
         <v>6</v>
       </c>
       <c r="H85" s="12"/>
@@ -5573,36 +5611,36 @@
       </c>
     </row>
     <row r="86" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A86" s="27"/>
-      <c r="B86" s="22"/>
+      <c r="A86" s="30"/>
+      <c r="B86" s="33"/>
       <c r="C86" s="10" t="s">
         <v>101</v>
       </c>
       <c r="D86" s="10">
         <v>3</v>
       </c>
-      <c r="E86" s="30"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="22"/>
+      <c r="E86" s="33"/>
+      <c r="F86" s="37"/>
+      <c r="G86" s="33"/>
       <c r="H86" s="12"/>
       <c r="I86" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A87" s="27">
+      <c r="A87" s="30">
         <v>46344</v>
       </c>
-      <c r="B87" s="22"/>
+      <c r="B87" s="33"/>
       <c r="C87" s="10" t="s">
         <v>102</v>
       </c>
       <c r="D87" s="10">
         <v>3</v>
       </c>
-      <c r="E87" s="30"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="22">
+      <c r="E87" s="33"/>
+      <c r="F87" s="37"/>
+      <c r="G87" s="33">
         <v>6</v>
       </c>
       <c r="H87" s="12"/>
@@ -5611,43 +5649,43 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A88" s="27"/>
-      <c r="B88" s="22"/>
+      <c r="A88" s="30"/>
+      <c r="B88" s="33"/>
       <c r="C88" s="10" t="s">
         <v>103</v>
       </c>
       <c r="D88" s="10">
         <v>3</v>
       </c>
-      <c r="E88" s="30"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="22"/>
+      <c r="E88" s="33"/>
+      <c r="F88" s="37"/>
+      <c r="G88" s="33"/>
       <c r="H88" s="12"/>
       <c r="I88" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A89" s="27">
+      <c r="A89" s="30">
         <v>46345</v>
       </c>
-      <c r="B89" s="22" t="s">
+      <c r="B89" s="33" t="s">
         <v>104</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D89" s="24">
-        <v>3</v>
-      </c>
-      <c r="E89" s="31">
+      <c r="D89" s="15">
+        <v>3</v>
+      </c>
+      <c r="E89" s="34">
         <f>SUM(D89:D100)</f>
         <v>36</v>
       </c>
-      <c r="F89" s="36" t="s">
+      <c r="F89" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="G89" s="22">
+      <c r="G89" s="33">
         <v>6</v>
       </c>
       <c r="H89" s="11"/>
@@ -5656,844 +5694,844 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A90" s="29"/>
-      <c r="B90" s="22"/>
+      <c r="A90" s="28"/>
+      <c r="B90" s="33"/>
       <c r="C90" s="10" t="s">
         <v>106</v>
       </c>
       <c r="D90" s="9">
         <v>3</v>
       </c>
-      <c r="E90" s="32"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="25"/>
-      <c r="H90" s="39"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="36"/>
+      <c r="G90" s="39"/>
+      <c r="H90" s="20"/>
       <c r="I90" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A91" s="29">
+      <c r="A91" s="28">
         <v>46346</v>
       </c>
-      <c r="B91" s="22"/>
+      <c r="B91" s="33"/>
       <c r="C91" s="10" t="s">
         <v>107</v>
       </c>
       <c r="D91" s="9">
         <v>3</v>
       </c>
-      <c r="E91" s="30"/>
-      <c r="F91" s="36"/>
-      <c r="G91" s="26">
+      <c r="E91" s="33"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="29">
         <v>6</v>
       </c>
-      <c r="H91" s="40"/>
+      <c r="H91" s="21"/>
       <c r="I91" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A92" s="29"/>
-      <c r="B92" s="22"/>
+      <c r="A92" s="28"/>
+      <c r="B92" s="33"/>
       <c r="C92" s="11" t="s">
         <v>108</v>
       </c>
       <c r="D92" s="9">
         <v>3</v>
       </c>
-      <c r="E92" s="33"/>
-      <c r="F92" s="36"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="40"/>
+      <c r="E92" s="31"/>
+      <c r="F92" s="32"/>
+      <c r="G92" s="29"/>
+      <c r="H92" s="21"/>
       <c r="I92" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A93" s="29">
+      <c r="A93" s="28">
         <v>46349</v>
       </c>
-      <c r="B93" s="22"/>
+      <c r="B93" s="33"/>
       <c r="C93" s="10" t="s">
         <v>109</v>
       </c>
       <c r="D93" s="9">
         <v>3</v>
       </c>
-      <c r="E93" s="33"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="26">
+      <c r="E93" s="31"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="29">
         <v>6</v>
       </c>
-      <c r="H93" s="41"/>
+      <c r="H93" s="16"/>
       <c r="I93" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A94" s="29"/>
-      <c r="B94" s="27"/>
+      <c r="A94" s="28"/>
+      <c r="B94" s="30"/>
       <c r="C94" s="10" t="s">
         <v>110</v>
       </c>
       <c r="D94" s="9">
         <v>3</v>
       </c>
-      <c r="E94" s="30"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="28"/>
-      <c r="H94" s="41"/>
+      <c r="E94" s="33"/>
+      <c r="F94" s="37"/>
+      <c r="G94" s="38"/>
+      <c r="H94" s="16"/>
       <c r="I94" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A95" s="29">
+      <c r="A95" s="28">
         <v>46350</v>
       </c>
-      <c r="B95" s="27"/>
+      <c r="B95" s="30"/>
       <c r="C95" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D95" s="24">
-        <v>3</v>
-      </c>
-      <c r="E95" s="33"/>
-      <c r="F95" s="36"/>
-      <c r="G95" s="26">
+      <c r="D95" s="15">
+        <v>3</v>
+      </c>
+      <c r="E95" s="31"/>
+      <c r="F95" s="32"/>
+      <c r="G95" s="29">
         <v>6</v>
       </c>
-      <c r="H95" s="41"/>
+      <c r="H95" s="16"/>
       <c r="I95" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A96" s="29"/>
-      <c r="B96" s="27"/>
+      <c r="A96" s="28"/>
+      <c r="B96" s="30"/>
       <c r="C96" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D96" s="24">
-        <v>3</v>
-      </c>
-      <c r="E96" s="33"/>
-      <c r="F96" s="36"/>
-      <c r="G96" s="26"/>
-      <c r="H96" s="41"/>
+      <c r="D96" s="15">
+        <v>3</v>
+      </c>
+      <c r="E96" s="31"/>
+      <c r="F96" s="32"/>
+      <c r="G96" s="29"/>
+      <c r="H96" s="16"/>
       <c r="I96" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A97" s="29">
+      <c r="A97" s="28">
         <v>46351</v>
       </c>
-      <c r="B97" s="27"/>
+      <c r="B97" s="30"/>
       <c r="C97" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="D97" s="24">
-        <v>3</v>
-      </c>
-      <c r="E97" s="30"/>
-      <c r="F97" s="36"/>
-      <c r="G97" s="26">
+      <c r="D97" s="15">
+        <v>3</v>
+      </c>
+      <c r="E97" s="33"/>
+      <c r="F97" s="32"/>
+      <c r="G97" s="29">
         <v>6</v>
       </c>
-      <c r="H97" s="41"/>
+      <c r="H97" s="16"/>
       <c r="I97" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A98" s="29"/>
-      <c r="B98" s="22"/>
+      <c r="A98" s="28"/>
+      <c r="B98" s="33"/>
       <c r="C98" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D98" s="24">
-        <v>3</v>
-      </c>
-      <c r="E98" s="33"/>
-      <c r="F98" s="36"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="41"/>
+      <c r="D98" s="15">
+        <v>3</v>
+      </c>
+      <c r="E98" s="31"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="16"/>
       <c r="I98" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A99" s="29">
+      <c r="A99" s="28">
         <v>46352</v>
       </c>
-      <c r="B99" s="27"/>
+      <c r="B99" s="30"/>
       <c r="C99" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D99" s="24">
-        <v>3</v>
-      </c>
-      <c r="E99" s="33"/>
-      <c r="F99" s="36"/>
-      <c r="G99" s="26">
+      <c r="D99" s="15">
+        <v>3</v>
+      </c>
+      <c r="E99" s="31"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="29">
         <v>6</v>
       </c>
-      <c r="H99" s="41"/>
+      <c r="H99" s="16"/>
       <c r="I99" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A100" s="29"/>
-      <c r="B100" s="27"/>
+      <c r="A100" s="28"/>
+      <c r="B100" s="30"/>
       <c r="C100" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D100" s="24">
-        <v>3</v>
-      </c>
-      <c r="E100" s="33"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="26"/>
-      <c r="H100" s="41"/>
+      <c r="D100" s="15">
+        <v>3</v>
+      </c>
+      <c r="E100" s="31"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="29"/>
+      <c r="H100" s="16"/>
       <c r="I100" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A101" s="29">
+      <c r="A101" s="28">
         <v>46353</v>
       </c>
-      <c r="B101" s="27" t="s">
+      <c r="B101" s="30" t="s">
         <v>117</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D101" s="24">
-        <v>3</v>
-      </c>
-      <c r="E101" s="33">
+      <c r="D101" s="15">
+        <v>3</v>
+      </c>
+      <c r="E101" s="31">
         <f>SUM(D101:D108)</f>
         <v>24</v>
       </c>
-      <c r="F101" s="36" t="s">
+      <c r="F101" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="G101" s="26">
+      <c r="G101" s="29">
         <v>6</v>
       </c>
-      <c r="H101" s="41"/>
+      <c r="H101" s="16"/>
       <c r="I101" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A102" s="29"/>
-      <c r="B102" s="27"/>
+      <c r="A102" s="28"/>
+      <c r="B102" s="30"/>
       <c r="C102" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D102" s="24">
-        <v>3</v>
-      </c>
-      <c r="E102" s="33"/>
-      <c r="F102" s="36"/>
-      <c r="G102" s="26"/>
-      <c r="H102" s="41"/>
+      <c r="D102" s="15">
+        <v>3</v>
+      </c>
+      <c r="E102" s="31"/>
+      <c r="F102" s="32"/>
+      <c r="G102" s="29"/>
+      <c r="H102" s="16"/>
       <c r="I102" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A103" s="29">
+      <c r="A103" s="28">
         <v>46356</v>
       </c>
-      <c r="B103" s="27"/>
+      <c r="B103" s="30"/>
       <c r="C103" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="24">
-        <v>3</v>
-      </c>
-      <c r="E103" s="33"/>
-      <c r="F103" s="36"/>
-      <c r="G103" s="26">
+      <c r="D103" s="15">
+        <v>3</v>
+      </c>
+      <c r="E103" s="31"/>
+      <c r="F103" s="32"/>
+      <c r="G103" s="29">
         <v>6</v>
       </c>
-      <c r="H103" s="41"/>
+      <c r="H103" s="16"/>
       <c r="I103" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A104" s="29"/>
-      <c r="B104" s="27"/>
+      <c r="A104" s="28"/>
+      <c r="B104" s="30"/>
       <c r="C104" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="D104" s="24">
-        <v>3</v>
-      </c>
-      <c r="E104" s="30"/>
-      <c r="F104" s="36"/>
-      <c r="G104" s="26"/>
-      <c r="H104" s="41"/>
+      <c r="D104" s="15">
+        <v>3</v>
+      </c>
+      <c r="E104" s="33"/>
+      <c r="F104" s="32"/>
+      <c r="G104" s="29"/>
+      <c r="H104" s="16"/>
       <c r="I104" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A105" s="29">
+      <c r="A105" s="28">
         <v>46357</v>
       </c>
-      <c r="B105" s="27"/>
+      <c r="B105" s="30"/>
       <c r="C105" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D105" s="24">
-        <v>3</v>
-      </c>
-      <c r="E105" s="30"/>
-      <c r="F105" s="36"/>
-      <c r="G105" s="26">
+      <c r="D105" s="15">
+        <v>3</v>
+      </c>
+      <c r="E105" s="33"/>
+      <c r="F105" s="32"/>
+      <c r="G105" s="29">
         <v>6</v>
       </c>
-      <c r="H105" s="41"/>
+      <c r="H105" s="16"/>
       <c r="I105" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A106" s="29"/>
-      <c r="B106" s="27"/>
+      <c r="A106" s="28"/>
+      <c r="B106" s="30"/>
       <c r="C106" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D106" s="24">
-        <v>3</v>
-      </c>
-      <c r="E106" s="30"/>
-      <c r="F106" s="36"/>
-      <c r="G106" s="26"/>
-      <c r="H106" s="41"/>
+      <c r="D106" s="15">
+        <v>3</v>
+      </c>
+      <c r="E106" s="33"/>
+      <c r="F106" s="32"/>
+      <c r="G106" s="29"/>
+      <c r="H106" s="16"/>
       <c r="I106" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A107" s="29">
+      <c r="A107" s="28">
         <v>46358</v>
       </c>
-      <c r="B107" s="27"/>
+      <c r="B107" s="30"/>
       <c r="C107" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D107" s="24">
-        <v>3</v>
-      </c>
-      <c r="E107" s="30"/>
-      <c r="F107" s="36"/>
-      <c r="G107" s="26">
+      <c r="D107" s="15">
+        <v>3</v>
+      </c>
+      <c r="E107" s="33"/>
+      <c r="F107" s="32"/>
+      <c r="G107" s="29">
         <v>6</v>
       </c>
-      <c r="H107" s="41"/>
+      <c r="H107" s="16"/>
       <c r="I107" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A108" s="29"/>
-      <c r="B108" s="27"/>
+      <c r="A108" s="28"/>
+      <c r="B108" s="30"/>
       <c r="C108" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D108" s="24">
-        <v>3</v>
-      </c>
-      <c r="E108" s="30"/>
-      <c r="F108" s="36"/>
-      <c r="G108" s="26"/>
-      <c r="H108" s="41"/>
+      <c r="D108" s="15">
+        <v>3</v>
+      </c>
+      <c r="E108" s="33"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="29"/>
+      <c r="H108" s="16"/>
       <c r="I108" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A109" s="29">
+      <c r="A109" s="28">
         <v>46359</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="30" t="s">
         <v>126</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D109" s="24">
-        <v>3</v>
-      </c>
-      <c r="E109" s="30">
+      <c r="D109" s="15">
+        <v>3</v>
+      </c>
+      <c r="E109" s="33">
         <f>SUM(D109:D116)</f>
         <v>24</v>
       </c>
-      <c r="F109" s="36" t="s">
+      <c r="F109" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="G109" s="26">
+      <c r="G109" s="29">
         <v>6</v>
       </c>
-      <c r="H109" s="41"/>
+      <c r="H109" s="16"/>
       <c r="I109" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A110" s="29"/>
-      <c r="B110" s="27"/>
+      <c r="A110" s="28"/>
+      <c r="B110" s="30"/>
       <c r="C110" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D110" s="24">
-        <v>3</v>
-      </c>
-      <c r="E110" s="30"/>
-      <c r="F110" s="36"/>
-      <c r="G110" s="26"/>
-      <c r="H110" s="41"/>
+      <c r="D110" s="15">
+        <v>3</v>
+      </c>
+      <c r="E110" s="33"/>
+      <c r="F110" s="32"/>
+      <c r="G110" s="29"/>
+      <c r="H110" s="16"/>
       <c r="I110" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A111" s="29">
+      <c r="A111" s="28">
         <v>46360</v>
       </c>
-      <c r="B111" s="27"/>
+      <c r="B111" s="30"/>
       <c r="C111" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D111" s="24">
-        <v>3</v>
-      </c>
-      <c r="E111" s="30"/>
-      <c r="F111" s="36"/>
-      <c r="G111" s="26">
+      <c r="D111" s="15">
+        <v>3</v>
+      </c>
+      <c r="E111" s="33"/>
+      <c r="F111" s="32"/>
+      <c r="G111" s="29">
         <v>6</v>
       </c>
-      <c r="H111" s="41"/>
+      <c r="H111" s="16"/>
       <c r="I111" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A112" s="29"/>
-      <c r="B112" s="27"/>
+      <c r="A112" s="28"/>
+      <c r="B112" s="30"/>
       <c r="C112" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D112" s="24">
-        <v>3</v>
-      </c>
-      <c r="E112" s="30"/>
-      <c r="F112" s="36"/>
-      <c r="G112" s="26"/>
-      <c r="H112" s="41"/>
+      <c r="D112" s="15">
+        <v>3</v>
+      </c>
+      <c r="E112" s="33"/>
+      <c r="F112" s="32"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="16"/>
       <c r="I112" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A113" s="29">
+      <c r="A113" s="28">
         <v>46363</v>
       </c>
-      <c r="B113" s="27"/>
+      <c r="B113" s="30"/>
       <c r="C113" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="D113" s="24">
-        <v>3</v>
-      </c>
-      <c r="E113" s="30"/>
-      <c r="F113" s="36"/>
-      <c r="G113" s="26">
+      <c r="D113" s="15">
+        <v>3</v>
+      </c>
+      <c r="E113" s="33"/>
+      <c r="F113" s="32"/>
+      <c r="G113" s="29">
         <v>6</v>
       </c>
-      <c r="H113" s="41"/>
+      <c r="H113" s="16"/>
       <c r="I113" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A114" s="29"/>
-      <c r="B114" s="27"/>
+      <c r="A114" s="28"/>
+      <c r="B114" s="30"/>
       <c r="C114" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D114" s="24">
-        <v>3</v>
-      </c>
-      <c r="E114" s="30"/>
-      <c r="F114" s="36"/>
-      <c r="G114" s="26"/>
-      <c r="H114" s="41"/>
+      <c r="D114" s="15">
+        <v>3</v>
+      </c>
+      <c r="E114" s="33"/>
+      <c r="F114" s="32"/>
+      <c r="G114" s="29"/>
+      <c r="H114" s="16"/>
       <c r="I114" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A115" s="29">
+      <c r="A115" s="28">
         <v>46364</v>
       </c>
-      <c r="B115" s="27"/>
+      <c r="B115" s="30"/>
       <c r="C115" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="24">
-        <v>3</v>
-      </c>
-      <c r="E115" s="30"/>
-      <c r="F115" s="36"/>
-      <c r="G115" s="26">
+      <c r="D115" s="15">
+        <v>3</v>
+      </c>
+      <c r="E115" s="33"/>
+      <c r="F115" s="32"/>
+      <c r="G115" s="29">
         <v>6</v>
       </c>
-      <c r="H115" s="41"/>
+      <c r="H115" s="16"/>
       <c r="I115" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A116" s="29"/>
-      <c r="B116" s="27"/>
+      <c r="A116" s="28"/>
+      <c r="B116" s="30"/>
       <c r="C116" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="D116" s="24">
-        <v>3</v>
-      </c>
-      <c r="E116" s="30"/>
-      <c r="F116" s="36"/>
-      <c r="G116" s="26"/>
-      <c r="H116" s="41"/>
+      <c r="D116" s="15">
+        <v>3</v>
+      </c>
+      <c r="E116" s="33"/>
+      <c r="F116" s="32"/>
+      <c r="G116" s="29"/>
+      <c r="H116" s="16"/>
       <c r="I116" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A117" s="29">
+      <c r="A117" s="28">
         <v>46365</v>
       </c>
-      <c r="B117" s="27" t="s">
+      <c r="B117" s="30" t="s">
         <v>135</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D117" s="24">
-        <v>3</v>
-      </c>
-      <c r="E117" s="30">
+      <c r="D117" s="15">
+        <v>3</v>
+      </c>
+      <c r="E117" s="33">
         <f>SUM(D117:D124)</f>
         <v>24</v>
       </c>
-      <c r="F117" s="36" t="s">
+      <c r="F117" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="G117" s="26">
+      <c r="G117" s="29">
         <v>6</v>
       </c>
-      <c r="H117" s="41"/>
+      <c r="H117" s="16"/>
       <c r="I117" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A118" s="29"/>
-      <c r="B118" s="27"/>
+      <c r="A118" s="28"/>
+      <c r="B118" s="30"/>
       <c r="C118" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="D118" s="24">
-        <v>3</v>
-      </c>
-      <c r="E118" s="30"/>
-      <c r="F118" s="36"/>
-      <c r="G118" s="26"/>
-      <c r="H118" s="41"/>
+      <c r="D118" s="15">
+        <v>3</v>
+      </c>
+      <c r="E118" s="33"/>
+      <c r="F118" s="32"/>
+      <c r="G118" s="29"/>
+      <c r="H118" s="16"/>
       <c r="I118" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A119" s="29">
+      <c r="A119" s="28">
         <v>46366</v>
       </c>
-      <c r="B119" s="27"/>
+      <c r="B119" s="30"/>
       <c r="C119" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D119" s="24">
-        <v>3</v>
-      </c>
-      <c r="E119" s="33"/>
-      <c r="F119" s="36"/>
-      <c r="G119" s="26">
+      <c r="D119" s="15">
+        <v>3</v>
+      </c>
+      <c r="E119" s="31"/>
+      <c r="F119" s="32"/>
+      <c r="G119" s="29">
         <v>6</v>
       </c>
-      <c r="H119" s="41"/>
+      <c r="H119" s="16"/>
       <c r="I119" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A120" s="29"/>
-      <c r="B120" s="27"/>
+      <c r="A120" s="28"/>
+      <c r="B120" s="30"/>
       <c r="C120" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D120" s="24">
-        <v>3</v>
-      </c>
-      <c r="E120" s="33"/>
-      <c r="F120" s="36"/>
-      <c r="G120" s="26"/>
-      <c r="H120" s="41"/>
+      <c r="D120" s="15">
+        <v>3</v>
+      </c>
+      <c r="E120" s="31"/>
+      <c r="F120" s="32"/>
+      <c r="G120" s="29"/>
+      <c r="H120" s="16"/>
       <c r="I120" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A121" s="29">
+      <c r="A121" s="28">
         <v>46367</v>
       </c>
-      <c r="B121" s="27"/>
+      <c r="B121" s="30"/>
       <c r="C121" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D121" s="24">
-        <v>3</v>
-      </c>
-      <c r="E121" s="33"/>
-      <c r="F121" s="36"/>
-      <c r="G121" s="26">
+      <c r="D121" s="15">
+        <v>3</v>
+      </c>
+      <c r="E121" s="31"/>
+      <c r="F121" s="32"/>
+      <c r="G121" s="29">
         <v>6</v>
       </c>
-      <c r="H121" s="41"/>
+      <c r="H121" s="16"/>
       <c r="I121" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A122" s="29"/>
-      <c r="B122" s="27"/>
+      <c r="A122" s="28"/>
+      <c r="B122" s="30"/>
       <c r="C122" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D122" s="24">
-        <v>3</v>
-      </c>
-      <c r="E122" s="33"/>
-      <c r="F122" s="36"/>
-      <c r="G122" s="26"/>
-      <c r="H122" s="41"/>
+      <c r="D122" s="15">
+        <v>3</v>
+      </c>
+      <c r="E122" s="31"/>
+      <c r="F122" s="32"/>
+      <c r="G122" s="29"/>
+      <c r="H122" s="16"/>
       <c r="I122" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A123" s="29">
+      <c r="A123" s="28">
         <v>46370</v>
       </c>
-      <c r="B123" s="27"/>
+      <c r="B123" s="30"/>
       <c r="C123" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D123" s="24">
-        <v>3</v>
-      </c>
-      <c r="E123" s="33"/>
-      <c r="F123" s="36"/>
-      <c r="G123" s="26">
+      <c r="D123" s="15">
+        <v>3</v>
+      </c>
+      <c r="E123" s="31"/>
+      <c r="F123" s="32"/>
+      <c r="G123" s="29">
         <v>6</v>
       </c>
-      <c r="H123" s="41"/>
+      <c r="H123" s="16"/>
       <c r="I123" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A124" s="29"/>
-      <c r="B124" s="27"/>
+      <c r="A124" s="28"/>
+      <c r="B124" s="30"/>
       <c r="C124" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="D124" s="24">
-        <v>3</v>
-      </c>
-      <c r="E124" s="33"/>
-      <c r="F124" s="36"/>
-      <c r="G124" s="26"/>
-      <c r="H124" s="41"/>
+      <c r="D124" s="15">
+        <v>3</v>
+      </c>
+      <c r="E124" s="31"/>
+      <c r="F124" s="32"/>
+      <c r="G124" s="29"/>
+      <c r="H124" s="16"/>
       <c r="I124" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A125" s="29">
+      <c r="A125" s="28">
         <v>46371</v>
       </c>
-      <c r="B125" s="27" t="s">
+      <c r="B125" s="30" t="s">
         <v>144</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D125" s="24">
-        <v>3</v>
-      </c>
-      <c r="E125" s="33">
+      <c r="D125" s="15">
+        <v>3</v>
+      </c>
+      <c r="E125" s="31">
         <f>SUM(D125:D132)</f>
         <v>24</v>
       </c>
-      <c r="F125" s="36" t="s">
+      <c r="F125" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="G125" s="26">
+      <c r="G125" s="29">
         <v>6</v>
       </c>
-      <c r="H125" s="41"/>
+      <c r="H125" s="16"/>
       <c r="I125" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A126" s="29"/>
-      <c r="B126" s="27"/>
+      <c r="A126" s="28"/>
+      <c r="B126" s="30"/>
       <c r="C126" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D126" s="24">
-        <v>3</v>
-      </c>
-      <c r="E126" s="33"/>
-      <c r="F126" s="36"/>
-      <c r="G126" s="26"/>
-      <c r="H126" s="41"/>
+      <c r="D126" s="15">
+        <v>3</v>
+      </c>
+      <c r="E126" s="31"/>
+      <c r="F126" s="32"/>
+      <c r="G126" s="29"/>
+      <c r="H126" s="16"/>
       <c r="I126" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A127" s="29">
+      <c r="A127" s="28">
         <v>46372</v>
       </c>
-      <c r="B127" s="27"/>
+      <c r="B127" s="30"/>
       <c r="C127" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D127" s="24">
-        <v>3</v>
-      </c>
-      <c r="E127" s="33"/>
-      <c r="F127" s="36"/>
-      <c r="G127" s="26">
+      <c r="D127" s="15">
+        <v>3</v>
+      </c>
+      <c r="E127" s="31"/>
+      <c r="F127" s="32"/>
+      <c r="G127" s="29">
         <v>6</v>
       </c>
-      <c r="H127" s="41"/>
+      <c r="H127" s="16"/>
       <c r="I127" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A128" s="29"/>
-      <c r="B128" s="27"/>
+      <c r="A128" s="28"/>
+      <c r="B128" s="30"/>
       <c r="C128" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D128" s="24">
-        <v>3</v>
-      </c>
-      <c r="E128" s="33"/>
-      <c r="F128" s="36"/>
-      <c r="G128" s="26"/>
-      <c r="H128" s="41"/>
+      <c r="D128" s="15">
+        <v>3</v>
+      </c>
+      <c r="E128" s="31"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="29"/>
+      <c r="H128" s="16"/>
       <c r="I128" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A129" s="29">
+      <c r="A129" s="28">
         <v>46373</v>
       </c>
-      <c r="B129" s="27"/>
+      <c r="B129" s="30"/>
       <c r="C129" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D129" s="24">
-        <v>3</v>
-      </c>
-      <c r="E129" s="33"/>
-      <c r="F129" s="36"/>
-      <c r="G129" s="26">
+      <c r="D129" s="15">
+        <v>3</v>
+      </c>
+      <c r="E129" s="31"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="29">
         <v>6</v>
       </c>
-      <c r="H129" s="41"/>
+      <c r="H129" s="16"/>
       <c r="I129" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A130" s="29"/>
-      <c r="B130" s="27"/>
+      <c r="A130" s="28"/>
+      <c r="B130" s="30"/>
       <c r="C130" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D130" s="24">
-        <v>3</v>
-      </c>
-      <c r="E130" s="33"/>
-      <c r="F130" s="36"/>
-      <c r="G130" s="26"/>
-      <c r="H130" s="41"/>
+      <c r="D130" s="15">
+        <v>3</v>
+      </c>
+      <c r="E130" s="31"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="29"/>
+      <c r="H130" s="16"/>
       <c r="I130" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A131" s="29">
+      <c r="A131" s="28">
         <v>46374</v>
       </c>
-      <c r="B131" s="27"/>
+      <c r="B131" s="30"/>
       <c r="C131" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D131" s="24">
-        <v>3</v>
-      </c>
-      <c r="E131" s="33"/>
-      <c r="F131" s="36"/>
-      <c r="G131" s="26">
+      <c r="D131" s="15">
+        <v>3</v>
+      </c>
+      <c r="E131" s="31"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="29">
         <v>6</v>
       </c>
-      <c r="H131" s="41"/>
+      <c r="H131" s="16"/>
       <c r="I131" s="14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A132" s="29"/>
-      <c r="B132" s="27"/>
+      <c r="A132" s="28"/>
+      <c r="B132" s="30"/>
       <c r="C132" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="D132" s="24">
-        <v>3</v>
-      </c>
-      <c r="E132" s="33"/>
-      <c r="F132" s="36"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="41"/>
+      <c r="D132" s="15">
+        <v>3</v>
+      </c>
+      <c r="E132" s="31"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="29"/>
+      <c r="H132" s="16"/>
       <c r="I132" s="14" t="b">
         <v>0</v>
       </c>
@@ -6534,16 +6572,16 @@
       <c r="H135"/>
     </row>
     <row r="136" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B136" s="19"/>
-      <c r="C136" s="20"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="17"/>
-      <c r="F136" s="17"/>
-      <c r="G136" s="17"/>
-      <c r="H136" s="18"/>
+      <c r="B136" s="23"/>
+      <c r="C136" s="24"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="26"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="26"/>
+      <c r="H136" s="27"/>
     </row>
     <row r="137" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B137"/>
@@ -6611,95 +6649,76 @@
     </row>
     <row r="146" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <mergeCells count="168">
-    <mergeCell ref="A136:H136"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="G129:G130"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="B125:B132"/>
-    <mergeCell ref="E125:E132"/>
-    <mergeCell ref="F125:F132"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="G125:G126"/>
-    <mergeCell ref="B117:B124"/>
-    <mergeCell ref="E117:E124"/>
-    <mergeCell ref="F117:F124"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="G117:G118"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="G119:G120"/>
-    <mergeCell ref="B109:B116"/>
-    <mergeCell ref="E109:E116"/>
-    <mergeCell ref="F109:F116"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="G109:G110"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="G111:G112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="G113:G114"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="G105:G106"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="G107:G108"/>
-    <mergeCell ref="B101:B108"/>
-    <mergeCell ref="E101:E108"/>
-    <mergeCell ref="F101:F108"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="G97:G98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="G101:G102"/>
-    <mergeCell ref="B89:B100"/>
-    <mergeCell ref="E89:E100"/>
-    <mergeCell ref="F89:F100"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="G93:G94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="G89:G90"/>
-    <mergeCell ref="B75:B88"/>
-    <mergeCell ref="E75:E88"/>
-    <mergeCell ref="F75:F88"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="G79:G80"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="G77:G78"/>
-    <mergeCell ref="B67:B74"/>
-    <mergeCell ref="E67:E74"/>
-    <mergeCell ref="F67:F74"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="G71:G72"/>
+  <mergeCells count="175">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="E13:E20"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="E21:E34"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B35:B46"/>
+    <mergeCell ref="E35:E46"/>
+    <mergeCell ref="F35:F46"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="B47:B54"/>
+    <mergeCell ref="E47:E54"/>
+    <mergeCell ref="F47:F54"/>
     <mergeCell ref="A61:A62"/>
     <mergeCell ref="G61:G62"/>
     <mergeCell ref="A63:A64"/>
@@ -6718,68 +6737,94 @@
     <mergeCell ref="G57:G58"/>
     <mergeCell ref="A59:A60"/>
     <mergeCell ref="G59:G60"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="B47:B54"/>
-    <mergeCell ref="E47:E54"/>
-    <mergeCell ref="F47:F54"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B35:B46"/>
-    <mergeCell ref="E35:E46"/>
-    <mergeCell ref="F35:F46"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="B21:B34"/>
-    <mergeCell ref="E21:E34"/>
-    <mergeCell ref="F21:F34"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="B13:B20"/>
-    <mergeCell ref="E13:E20"/>
-    <mergeCell ref="F13:F20"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="B67:B74"/>
+    <mergeCell ref="E67:E74"/>
+    <mergeCell ref="F67:F74"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="G89:G90"/>
+    <mergeCell ref="B75:B88"/>
+    <mergeCell ref="E75:E88"/>
+    <mergeCell ref="F75:F88"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="G79:G80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="G101:G102"/>
+    <mergeCell ref="B89:B100"/>
+    <mergeCell ref="E89:E100"/>
+    <mergeCell ref="F89:F100"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="G103:G104"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="G105:G106"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="G107:G108"/>
+    <mergeCell ref="B101:B108"/>
+    <mergeCell ref="E101:E108"/>
+    <mergeCell ref="F101:F108"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="G117:G118"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="G119:G120"/>
+    <mergeCell ref="B109:B116"/>
+    <mergeCell ref="E109:E116"/>
+    <mergeCell ref="F109:F116"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="G111:G112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="G113:G114"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="G121:G122"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="G125:G126"/>
+    <mergeCell ref="B117:B124"/>
+    <mergeCell ref="E117:E124"/>
+    <mergeCell ref="F117:F124"/>
+    <mergeCell ref="A136:H136"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="G127:G128"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="G129:G130"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="B125:B132"/>
+    <mergeCell ref="E125:E132"/>
+    <mergeCell ref="F125:F132"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
